--- a/data/real_training_data.xlsx
+++ b/data/real_training_data.xlsx
@@ -710,22 +710,22 @@
         <v>13431436.28</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>54681406.96</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>6249303.65</v>
       </c>
       <c r="N2" t="n">
         <v>12218.85</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>4686977.74</v>
       </c>
       <c r="P2" t="n">
         <v>750072.11</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3905814.78</v>
       </c>
       <c r="R2" t="n">
         <v>4043898.6</v>
@@ -749,7 +749,7 @@
         <v>37847.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>6626.41</v>
       </c>
       <c r="Z2" t="n">
         <v>5374297.17</v>
@@ -809,7 +809,7 @@
         <v>0.4926</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>0.0954</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
@@ -867,22 +867,22 @@
         <v>8514280.279999999</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>31786409.4</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3632732.5</v>
       </c>
       <c r="N3" t="n">
         <v>1884577.3</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2724549.38</v>
       </c>
       <c r="P3" t="n">
         <v>3341698.44</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2270457.81</v>
       </c>
       <c r="R3" t="n">
         <v>2751702.63</v>
@@ -906,7 +906,7 @@
         <v>154301.98</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>6719.94</v>
       </c>
       <c r="Z3" t="n">
         <v>1340298.73</v>
@@ -966,7 +966,7 @@
         <v>0.2996</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>0.1017</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
@@ -1024,22 +1024,22 @@
         <v>52278056.23</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>300045800.35</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>34290948.61</v>
       </c>
       <c r="N4" t="n">
         <v>2332.78</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>25718211.46</v>
       </c>
       <c r="P4" t="n">
         <v>17151160.02</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>21431842.88</v>
       </c>
       <c r="R4" t="n">
         <v>11175293</v>
@@ -1063,7 +1063,7 @@
         <v>781452.61</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>33375.3</v>
       </c>
       <c r="Z4" t="n">
         <v>5274913.54</v>
@@ -1123,7 +1123,7 @@
         <v>0.6032999999999999</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>0.1107</v>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
@@ -1181,22 +1181,22 @@
         <v>7547642.11</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>13646268.97</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1559573.6</v>
       </c>
       <c r="N5" t="n">
         <v>28602.27</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1169680.2</v>
       </c>
       <c r="P5" t="n">
         <v>255523.01</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>974733.5</v>
       </c>
       <c r="R5" t="n">
         <v>1077874.44</v>
@@ -1220,7 +1220,7 @@
         <v>51225.69</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>3408.32</v>
       </c>
       <c r="Z5" t="n">
         <v>1994850.31</v>
@@ -1280,7 +1280,7 @@
         <v>1.0751</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>0.1643</v>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
@@ -1338,22 +1338,22 @@
         <v>37785259.84</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>170546683.91</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>19491049.59</v>
       </c>
       <c r="N6" t="n">
         <v>100724.75</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>14618287.19</v>
       </c>
       <c r="P6" t="n">
         <v>11968029.06</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>12181905.99</v>
       </c>
       <c r="R6" t="n">
         <v>2101531.77</v>
@@ -1377,7 +1377,7 @@
         <v>512235.2</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>167703.93</v>
       </c>
       <c r="Z6" t="n">
         <v>16518821.75</v>
@@ -1437,7 +1437,7 @@
         <v>0.4534</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>0.6685</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
@@ -1495,22 +1495,22 @@
         <v>51123172.49</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>127273556.69</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>14545549.34</v>
       </c>
       <c r="N7" t="n">
         <v>1832.58</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>10909162</v>
       </c>
       <c r="P7" t="n">
         <v>11004323.71</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>9090968.34</v>
       </c>
       <c r="R7" t="n">
         <v>11468978.75</v>
@@ -1534,7 +1534,7 @@
         <v>499718.75</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>13839.71</v>
       </c>
       <c r="Z7" t="n">
         <v>5230396.08</v>
@@ -1594,7 +1594,7 @@
         <v>0.3835</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>0.0597</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
@@ -1652,22 +1652,22 @@
         <v>10244534.34</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>44070105.48</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>5036583.48</v>
       </c>
       <c r="N8" t="n">
         <v>10993.1</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3777437.61</v>
       </c>
       <c r="P8" t="n">
         <v>523002.76</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3147864.68</v>
       </c>
       <c r="R8" t="n">
         <v>3121030.31</v>
@@ -1691,7 +1691,7 @@
         <v>16335.87</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>4614.76</v>
       </c>
       <c r="Z8" t="n">
         <v>4295213.09</v>
@@ -1751,7 +1751,7 @@
         <v>0.6307</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>0.1001</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
@@ -1809,22 +1809,22 @@
         <v>59482597.84</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>154983550.56</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>17712405.78</v>
       </c>
       <c r="N9" t="n">
         <v>8261.120000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>13284304.33</v>
       </c>
       <c r="P9" t="n">
         <v>12319276.32</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>11070253.61</v>
       </c>
       <c r="R9" t="n">
         <v>13690261.9</v>
@@ -1848,7 +1848,7 @@
         <v>674423.12</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>145940.51</v>
       </c>
       <c r="Z9" t="n">
         <v>5355797.79</v>
@@ -1908,7 +1908,7 @@
         <v>0.389</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>0.5377</v>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
@@ -1966,22 +1966,22 @@
         <v>23855319.96</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>46715424.64</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>5338905.67</v>
       </c>
       <c r="N10" t="n">
         <v>2453</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>4004179.25</v>
       </c>
       <c r="P10" t="n">
         <v>4323081.45</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3336816.05</v>
       </c>
       <c r="R10" t="n">
         <v>3638451.31</v>
@@ -2005,7 +2005,7 @@
         <v>115960.57</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>14551.96</v>
       </c>
       <c r="Z10" t="n">
         <v>9025323.470000001</v>
@@ -2065,7 +2065,7 @@
         <v>0.4134</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>0.1905</v>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
@@ -2123,22 +2123,22 @@
         <v>3645189.55</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>8271721.74</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>945339.63</v>
       </c>
       <c r="N11" t="n">
         <v>2438.15</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>709004.72</v>
       </c>
       <c r="P11" t="n">
         <v>608094.4300000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>590837.27</v>
       </c>
       <c r="R11" t="n">
         <v>770286.98</v>
@@ -2162,7 +2162,7 @@
         <v>34723.28</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>3956.93</v>
       </c>
       <c r="Z11" t="n">
         <v>710502.08</v>
@@ -2222,7 +2222,7 @@
         <v>0.2911</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>0.2447</v>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
@@ -2280,22 +2280,22 @@
         <v>15501530.68</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>30205658.94</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3452075.31</v>
       </c>
       <c r="N12" t="n">
         <v>101530.32</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2589056.48</v>
       </c>
       <c r="P12" t="n">
         <v>3170470.94</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2157547.07</v>
       </c>
       <c r="R12" t="n">
         <v>8896039.02</v>
@@ -2319,7 +2319,7 @@
         <v>83475.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>61691.09</v>
       </c>
       <c r="Z12" t="n">
         <v>858627.9300000001</v>
@@ -2379,7 +2379,7 @@
         <v>0.2579</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>1.0308</v>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
@@ -2437,22 +2437,22 @@
         <v>171101056.12</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>465129653.56</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>53157674.69</v>
       </c>
       <c r="N13" t="n">
         <v>240870.97</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>39868256.02</v>
       </c>
       <c r="P13" t="n">
         <v>35870713.73</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>33223546.68</v>
       </c>
       <c r="R13" t="n">
         <v>40760448.64</v>
@@ -2476,10 +2476,10 @@
         <v>1443074.75</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>73541.14999999999</v>
       </c>
       <c r="Z13" t="n">
-        <v>13863638.53</v>
+        <v>13853022.13</v>
       </c>
       <c r="AA13" t="n">
         <v>1339503.36</v>
@@ -2536,7 +2536,7 @@
         <v>0.3843</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>0.0892</v>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
@@ -2594,22 +2594,22 @@
         <v>20224582.09</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>81387065.87</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>9301378.960000001</v>
       </c>
       <c r="N14" t="n">
         <v>357449.92</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>6976034.22</v>
       </c>
       <c r="P14" t="n">
         <v>6112799.73</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>5813361.85</v>
       </c>
       <c r="R14" t="n">
         <v>6019136.65</v>
@@ -2633,7 +2633,7 @@
         <v>259888.16</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>11978.76</v>
       </c>
       <c r="Z14" t="n">
         <v>9483250.91</v>
@@ -2693,7 +2693,7 @@
         <v>0.4477</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>0.0983</v>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
@@ -2751,22 +2751,22 @@
         <v>40839088.91</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>179904128.65</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>20560471.85</v>
       </c>
       <c r="N15" t="n">
         <v>32148.72</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>15420353.88</v>
       </c>
       <c r="P15" t="n">
         <v>12573699.78</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>12850294.9</v>
       </c>
       <c r="R15" t="n">
         <v>13089211.47</v>
@@ -2790,7 +2790,7 @@
         <v>509502.29</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>19920.45</v>
       </c>
       <c r="Z15" t="n">
         <v>21957800.32</v>
@@ -2850,7 +2850,7 @@
         <v>0.4245</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>0.0752</v>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
@@ -2908,22 +2908,22 @@
         <v>6577945.99</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>12897077.86</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1473951.76</v>
       </c>
       <c r="N16" t="n">
         <v>2684.82</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1105463.82</v>
       </c>
       <c r="P16" t="n">
         <v>1196932.75</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>921219.85</v>
       </c>
       <c r="R16" t="n">
         <v>1051552.21</v>
@@ -2947,7 +2947,7 @@
         <v>39602.97</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>7637.62</v>
       </c>
       <c r="Z16" t="n">
         <v>2078046.18</v>
@@ -3007,7 +3007,7 @@
         <v>0.5153</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>0.3593</v>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
@@ -3065,22 +3065,22 @@
         <v>54165.16</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>173134.7</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>19786.82</v>
       </c>
       <c r="N17" t="n">
         <v>226129.46</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>14840.12</v>
       </c>
       <c r="P17" t="n">
         <v>227306.98</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>12366.76</v>
       </c>
       <c r="R17" t="n">
         <v>1334349.47</v>
@@ -3104,7 +3104,7 @@
         <v>54489.71</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>9.32</v>
       </c>
       <c r="Z17" t="n">
         <v>4357.3</v>
@@ -3164,7 +3164,7 @@
         <v>0.0058</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
@@ -3222,22 +3222,22 @@
         <v>15044084.89</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>76058396.97</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>8692388.220000001</v>
       </c>
       <c r="N18" t="n">
         <v>11976.21</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>6519291.17</v>
       </c>
       <c r="P18" t="n">
         <v>5206855.18</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>5432742.64</v>
       </c>
       <c r="R18" t="n">
         <v>5450537.08</v>
@@ -3261,7 +3261,7 @@
         <v>242156.21</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>11333.25</v>
       </c>
       <c r="Z18" t="n">
         <v>1416554.08</v>
@@ -3321,7 +3321,7 @@
         <v>0.6382</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>0.1275</v>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
@@ -3379,22 +3379,22 @@
         <v>85434359.03</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>242298891.37</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>27691301.87</v>
       </c>
       <c r="N19" t="n">
         <v>41696.35</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>20768476.4</v>
       </c>
       <c r="P19" t="n">
         <v>17512889.17</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>17307063.67</v>
       </c>
       <c r="R19" t="n">
         <v>68602361.86</v>
@@ -3418,10 +3418,10 @@
         <v>635088.5699999999</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>25983.35</v>
       </c>
       <c r="Z19" t="n">
-        <v>10709773.52</v>
+        <v>10707730.17</v>
       </c>
       <c r="AA19" t="n">
         <v>1488000.53</v>
@@ -3478,7 +3478,7 @@
         <v>0.3742</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>0.0563</v>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
@@ -3536,22 +3536,22 @@
         <v>21580260.65</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>68836152.76000001</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>7866988.89</v>
       </c>
       <c r="N20" t="n">
         <v>81352.61</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>5900241.67</v>
       </c>
       <c r="P20" t="n">
         <v>3812307.66</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4916868.05</v>
       </c>
       <c r="R20" t="n">
         <v>15368780.87</v>
@@ -3575,7 +3575,7 @@
         <v>154075.31</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>5549.67</v>
       </c>
       <c r="Z20" t="n">
         <v>7828117.08</v>
@@ -3635,7 +3635,7 @@
         <v>1.01</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>0.0537</v>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
@@ -3693,22 +3693,22 @@
         <v>21292651.37</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>39358847.9</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4498154.05</v>
       </c>
       <c r="N21" t="n">
         <v>1292.15</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3373615.53</v>
       </c>
       <c r="P21" t="n">
         <v>4179703.51</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2811346.28</v>
       </c>
       <c r="R21" t="n">
         <v>12618379.68</v>
@@ -3732,7 +3732,7 @@
         <v>154932.07</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>6125.81</v>
       </c>
       <c r="Z21" t="n">
         <v>5488677.1</v>
@@ -3792,7 +3792,7 @@
         <v>0.2722</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>0.0722</v>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
@@ -3850,22 +3850,22 @@
         <v>13548507.73</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>33236984.33</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3798512.49</v>
       </c>
       <c r="N22" t="n">
         <v>561334.14</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2848884.37</v>
       </c>
       <c r="P22" t="n">
         <v>3268094.15</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2374070.31</v>
       </c>
       <c r="R22" t="n">
         <v>9273001.939999999</v>
@@ -3889,7 +3889,7 @@
         <v>232655.45</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>5350.55</v>
       </c>
       <c r="Z22" t="n">
         <v>939183.1800000001</v>
@@ -3949,7 +3949,7 @@
         <v>0.4149</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>0.0785</v>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
@@ -4007,22 +4007,22 @@
         <v>30049334.22</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>99211929.3</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>11338506.21</v>
       </c>
       <c r="N23" t="n">
         <v>60417.78</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>8503879.65</v>
       </c>
       <c r="P23" t="n">
         <v>6201037.54</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>7086566.38</v>
       </c>
       <c r="R23" t="n">
         <v>25594779.49</v>
@@ -4046,7 +4046,7 @@
         <v>222151.63</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>4876.85</v>
       </c>
       <c r="Z23" t="n">
         <v>1820389.13</v>
@@ -4106,7 +4106,7 @@
         <v>0.4476</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>0.0283</v>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>“环境治理攻坚行动”青龙片区整治工程项目</t>
+          <t>环境治理攻坚行动”青龙片区整治工程项目</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4164,22 +4164,22 @@
         <v>11337834.63</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>40081476.83</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>4580740.21</v>
       </c>
       <c r="N24" t="n">
         <v>3161.01</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3435555.16</v>
       </c>
       <c r="P24" t="n">
         <v>1763525.36</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2862962.63</v>
       </c>
       <c r="R24" t="n">
         <v>8949890.220000001</v>
@@ -4203,7 +4203,7 @@
         <v>13509.29</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>7147.91</v>
       </c>
       <c r="Z24" t="n">
         <v>20381.91</v>
@@ -4263,7 +4263,7 @@
         <v>0.0965</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>0.1187</v>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
@@ -4321,22 +4321,22 @@
         <v>33345742.44</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>103575800.78</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>11837234.37</v>
       </c>
       <c r="N25" t="n">
         <v>991516.24</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>8877925.779999999</v>
       </c>
       <c r="P25" t="n">
         <v>5963742.36</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>7398271.48</v>
       </c>
       <c r="R25" t="n">
         <v>21328924.08</v>
@@ -4360,7 +4360,7 @@
         <v>145811.85</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>4012.06</v>
       </c>
       <c r="Z25" t="n">
         <v>1069396.1</v>
@@ -4420,7 +4420,7 @@
         <v>0.2539</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>0.0233</v>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
@@ -4478,22 +4478,22 @@
         <v>100643598.4</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>344519009.5</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>39373601.09</v>
       </c>
       <c r="N26" t="n">
         <v>40421.43</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>29530200.81</v>
       </c>
       <c r="P26" t="n">
         <v>19611428.43</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>24608500.68</v>
       </c>
       <c r="R26" t="n">
         <v>72525646.83</v>
@@ -4635,22 +4635,22 @@
         <v>116254878.35</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>497855608.26</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>56897783.8</v>
       </c>
       <c r="N27" t="n">
         <v>1597480.69</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>42673337.85</v>
       </c>
       <c r="P27" t="n">
         <v>21177150.68</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>35561114.88</v>
       </c>
       <c r="R27" t="n">
         <v>90375908.66</v>
@@ -4674,7 +4674,7 @@
         <v>848540.8199999999</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>88406.67</v>
       </c>
       <c r="Z27" t="n">
         <v>7137018.27</v>
@@ -4734,7 +4734,7 @@
         <v>0.3718</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>0.1212</v>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
@@ -4792,22 +4792,22 @@
         <v>106131153.01</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>381535257.89</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>43604029.47</v>
       </c>
       <c r="N28" t="n">
         <v>15178.8</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>32703022.1</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>27252518.42</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -4949,22 +4949,22 @@
         <v>6277060.87</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>27133639.54</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3100987.38</v>
       </c>
       <c r="N29" t="n">
         <v>1781.74</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2325740.53</v>
       </c>
       <c r="P29" t="n">
         <v>1970742.53</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1938117.11</v>
       </c>
       <c r="R29" t="n">
         <v>1961826.88</v>
@@ -4988,7 +4988,7 @@
         <v>2120.45</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>4567.74</v>
       </c>
       <c r="Z29" t="n">
         <v>2686259.25</v>
@@ -5048,7 +5048,7 @@
         <v>0.5053</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>0.1378</v>
       </c>
       <c r="AT29" t="inlineStr">
         <is>
@@ -5106,22 +5106,22 @@
         <v>1671325.55</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>7828528.94</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>894689.02</v>
       </c>
       <c r="N30" t="n">
         <v>699.46</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>671016.77</v>
       </c>
       <c r="P30" t="n">
         <v>595859.04</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>559180.64</v>
       </c>
       <c r="R30" t="n">
         <v>664732.46</v>
@@ -5145,7 +5145,7 @@
         <v>38113.26</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>3882.23</v>
       </c>
       <c r="Z30" t="n">
         <v>3876587.81</v>
@@ -5205,7 +5205,7 @@
         <v>0.0011</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>0.2848</v>
       </c>
       <c r="AT30" t="inlineStr">
         <is>
@@ -5263,22 +5263,22 @@
         <v>8240123.41</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>34808286.56</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3978089.89</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2983567.42</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2486306.18</v>
       </c>
       <c r="R31" t="n">
         <v>2971977.66</v>
@@ -5302,7 +5302,7 @@
         <v>395190.55</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>10937.82</v>
       </c>
       <c r="Z31" t="n">
         <v>5178107.62</v>
@@ -5362,7 +5362,7 @@
         <v>0.4344</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>0.1788</v>
       </c>
       <c r="AT31" t="inlineStr">
         <is>
@@ -5420,22 +5420,22 @@
         <v>3853758.68</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>16138400.22</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>1844388.6</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>1383291.45</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1152742.87</v>
       </c>
       <c r="R32" t="n">
         <v>1184062.96</v>
@@ -5459,7 +5459,7 @@
         <v>146086.19</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>25135.96</v>
       </c>
       <c r="Z32" t="n">
         <v>1821030.14</v>
@@ -5519,7 +5519,7 @@
         <v>0.6067</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AT32" t="inlineStr">
         <is>
@@ -5577,22 +5577,22 @@
         <v>13662119.68</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>35089027.27</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>4010174.55</v>
       </c>
       <c r="N33" t="n">
         <v>6424.79</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3007630.91</v>
       </c>
       <c r="P33" t="n">
         <v>2419436.35</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2506359.09</v>
       </c>
       <c r="R33" t="n">
         <v>8390823.99</v>
@@ -5616,7 +5616,7 @@
         <v>33057.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>571.51</v>
       </c>
       <c r="Z33" t="n">
         <v>3159549.59</v>
@@ -5676,7 +5676,7 @@
         <v>0.0138</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>0.0101</v>
       </c>
       <c r="AT33" t="inlineStr">
         <is>
@@ -5734,22 +5734,22 @@
         <v>73486551.76000001</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>258399060.84</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>29531321.24</v>
       </c>
       <c r="N34" t="n">
         <v>5842.19</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>22148490.93</v>
       </c>
       <c r="P34" t="n">
         <v>8379702.38</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>18457075.77</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -5891,22 +5891,22 @@
         <v>20819089.96</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>110397173.09</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>12616819.78</v>
       </c>
       <c r="N35" t="n">
         <v>137386.3</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>9462614.84</v>
       </c>
       <c r="P35" t="n">
         <v>3332429.94</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>7885512.36</v>
       </c>
       <c r="R35" t="n">
         <v>17171593.47</v>
@@ -5930,7 +5930,7 @@
         <v>80255.42999999999</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>2325.71</v>
       </c>
       <c r="Z35" t="n">
         <v>214539.62</v>
@@ -5990,7 +5990,7 @@
         <v>0.0535</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>0.0168</v>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
@@ -6048,22 +6048,22 @@
         <v>31126389.14</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>308427846.34</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>35248896.72</v>
       </c>
       <c r="N36" t="n">
         <v>15624.23</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>26436672.54</v>
       </c>
       <c r="P36" t="n">
         <v>7409474.28</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>22030560.45</v>
       </c>
       <c r="R36" t="n">
         <v>43514271.45</v>
@@ -6087,13 +6087,13 @@
         <v>476034.45</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>15793.84</v>
       </c>
       <c r="Z36" t="n">
         <v>319206.61</v>
       </c>
       <c r="AA36" t="n">
-        <v>236376.23</v>
+        <v>236328.51</v>
       </c>
       <c r="AB36" t="n">
         <v>2453.16</v>
@@ -6147,7 +6147,7 @@
         <v>0.191</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>0.0407</v>
       </c>
       <c r="AT36" t="inlineStr">
         <is>
@@ -6205,22 +6205,22 @@
         <v>40720288.25</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>317065002.87</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>36236000.33</v>
       </c>
       <c r="N37" t="n">
         <v>19740.21</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>27177000.25</v>
       </c>
       <c r="P37" t="n">
         <v>9737218.859999999</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>22647500.21</v>
       </c>
       <c r="R37" t="n">
         <v>48442752.07</v>
@@ -6244,7 +6244,7 @@
         <v>492015.38</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>12261.63</v>
       </c>
       <c r="Z37" t="n">
         <v>495785.99</v>
@@ -6304,7 +6304,7 @@
         <v>0.3028</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>0.044</v>
       </c>
       <c r="AT37" t="inlineStr">
         <is>
@@ -6362,22 +6362,22 @@
         <v>49118488.01</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>284193938.38</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>32479307.24</v>
       </c>
       <c r="N38" t="n">
         <v>5776.07</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>24359480.43</v>
       </c>
       <c r="P38" t="n">
         <v>10733545.3</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>20299567.03</v>
       </c>
       <c r="R38" t="n">
         <v>44652552</v>
@@ -6401,7 +6401,7 @@
         <v>461274.79</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>14340.46</v>
       </c>
       <c r="Z38" t="n">
         <v>3217204.77</v>
@@ -6461,7 +6461,7 @@
         <v>0.208</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>0.0351</v>
       </c>
       <c r="AT38" t="inlineStr">
         <is>
@@ -6519,22 +6519,22 @@
         <v>94011675.41</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>254739729.91</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>29113111.99</v>
       </c>
       <c r="N39" t="n">
         <v>16514.63</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>21834833.99</v>
       </c>
       <c r="P39" t="n">
         <v>12091416.76</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>18195694.99</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -6676,22 +6676,22 @@
         <v>4177374.39</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>20387476.86</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>2329997.36</v>
       </c>
       <c r="N40" t="n">
         <v>92329.67</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>1747498.02</v>
       </c>
       <c r="P40" t="n">
         <v>197851.63</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>1456248.35</v>
       </c>
       <c r="R40" t="n">
         <v>1359118.48</v>
@@ -6715,7 +6715,7 @@
         <v>78767.06</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>13570.54</v>
       </c>
       <c r="Z40" t="n">
         <v>1670329.98</v>
@@ -6775,7 +6775,7 @@
         <v>0.9157</v>
       </c>
       <c r="AS40" t="n">
-        <v>0</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="AT40" t="inlineStr">
         <is>
@@ -6833,22 +6833,22 @@
         <v>6618958.91</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>36948353.28</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>4222668.95</v>
       </c>
       <c r="N41" t="n">
         <v>26385.09</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3167001.71</v>
       </c>
       <c r="P41" t="n">
         <v>2311532.61</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>2639168.09</v>
       </c>
       <c r="R41" t="n">
         <v>2578280.44</v>
@@ -6872,7 +6872,7 @@
         <v>96005.58</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>23391.26</v>
       </c>
       <c r="Z41" t="n">
         <v>981342.23</v>
@@ -6932,7 +6932,7 @@
         <v>0.7498</v>
       </c>
       <c r="AS41" t="n">
-        <v>0</v>
+        <v>0.895</v>
       </c>
       <c r="AT41" t="inlineStr">
         <is>
@@ -6990,22 +6990,22 @@
         <v>57762443.31</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>174466075.12</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>19938980.01</v>
       </c>
       <c r="N42" t="n">
         <v>2583.99</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>14954235.01</v>
       </c>
       <c r="P42" t="n">
         <v>5231090.25</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>12461862.51</v>
       </c>
       <c r="R42" t="n">
         <v>31302276.12</v>
@@ -7029,7 +7029,7 @@
         <v>327887.32</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>415667.03</v>
       </c>
       <c r="Z42" t="n">
         <v>762374.45</v>
@@ -7089,7 +7089,7 @@
         <v>0.3548</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>1.6337</v>
       </c>
       <c r="AT42" t="inlineStr">
         <is>
@@ -7147,22 +7147,22 @@
         <v>9101005.710000001</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>33750520.09</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3857202.3</v>
       </c>
       <c r="N43" t="n">
         <v>15061.64</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>2892901.72</v>
       </c>
       <c r="P43" t="n">
         <v>1033613.17</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>2410751.44</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -7304,22 +7304,22 @@
         <v>8444875.74</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>42876647.46</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>4900188.28</v>
       </c>
       <c r="N44" t="n">
         <v>64438.73</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3675141.21</v>
       </c>
       <c r="P44" t="n">
         <v>2626220.26</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3062617.68</v>
       </c>
       <c r="R44" t="n">
         <v>3032585.03</v>
@@ -7343,7 +7343,7 @@
         <v>124459.11</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>39656.78</v>
       </c>
       <c r="Z44" t="n">
         <v>3183280.84</v>
@@ -7403,7 +7403,7 @@
         <v>0.6709000000000001</v>
       </c>
       <c r="AS44" t="n">
-        <v>0</v>
+        <v>0.9454</v>
       </c>
       <c r="AT44" t="inlineStr">
         <is>
@@ -7461,22 +7461,22 @@
         <v>13481111.29</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>68470522.81</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>7825202.61</v>
       </c>
       <c r="N45" t="n">
         <v>10998.6</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>5868901.96</v>
       </c>
       <c r="P45" t="n">
         <v>4569722.96</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>4890751.63</v>
       </c>
       <c r="R45" t="n">
         <v>4866205.24</v>
@@ -7500,7 +7500,7 @@
         <v>188221.16</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>8792.48</v>
       </c>
       <c r="Z45" t="n">
         <v>898346.15</v>
@@ -7560,7 +7560,7 @@
         <v>0.6037</v>
       </c>
       <c r="AS45" t="n">
-        <v>0</v>
+        <v>0.1129</v>
       </c>
       <c r="AT45" t="inlineStr">
         <is>
@@ -7618,22 +7618,22 @@
         <v>19658889.06</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>86839951.87</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>9924565.93</v>
       </c>
       <c r="N46" t="n">
         <v>563250.7</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>7443424.45</v>
       </c>
       <c r="P46" t="n">
         <v>6438748.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>6202853.7</v>
       </c>
       <c r="R46" t="n">
         <v>6283236.2</v>
@@ -7657,7 +7657,7 @@
         <v>66411.32000000001</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>15364.26</v>
       </c>
       <c r="Z46" t="n">
         <v>7930215.96</v>
@@ -7717,7 +7717,7 @@
         <v>0.5377</v>
       </c>
       <c r="AS46" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="AT46" t="inlineStr">
         <is>
@@ -7775,22 +7775,22 @@
         <v>38048460.46</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>221032055.78</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>25260806.37</v>
       </c>
       <c r="N47" t="n">
         <v>898056.13</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>18945604.78</v>
       </c>
       <c r="P47" t="n">
         <v>13866747.19</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>15788003.98</v>
       </c>
       <c r="R47" t="n">
         <v>16578076.62</v>
@@ -7814,7 +7814,7 @@
         <v>787392.42</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>188076.46</v>
       </c>
       <c r="Z47" t="n">
         <v>4408640.93</v>
@@ -7874,7 +7874,7 @@
         <v>0.6639</v>
       </c>
       <c r="AS47" t="n">
-        <v>0</v>
+        <v>0.7725</v>
       </c>
       <c r="AT47" t="inlineStr">
         <is>
